--- a/data/bloodtype.xlsx
+++ b/data/bloodtype.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoba10\OneDrive\Desktop\reto\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9982775D-4D37-4C9D-BE09-B2168DE21C3F}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1680" windowWidth="14475" windowHeight="14520" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
+    <workbookView xWindow="9060" yWindow="1890" windowWidth="16155" windowHeight="13170" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4638,7 +4638,7 @@
         <v>384</v>
       </c>
       <c r="B379" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.4">

--- a/data/bloodtype.xlsx
+++ b/data/bloodtype.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9982775D-4D37-4C9D-BE09-B2168DE21C3F}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7556851-EC27-45F7-AE9F-B81C1ED17A8F}"/>
   <bookViews>
-    <workbookView xWindow="9060" yWindow="1890" windowWidth="16155" windowHeight="13170" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="404">
   <si>
     <t>ルフィ</t>
   </si>
@@ -1243,6 +1243,10 @@
   </si>
   <si>
     <t>コニー</t>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1307,6 +1311,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4078,7 +4086,7 @@
         <v>314</v>
       </c>
       <c r="B309" t="s">
-        <v>240</v>
+        <v>403</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.4">

--- a/data/bloodtype.xlsx
+++ b/data/bloodtype.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7556851-EC27-45F7-AE9F-B81C1ED17A8F}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E605AB9-02AD-4E4A-9D31-E27DB6801538}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="7980" windowHeight="13170" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="405">
   <si>
     <t>ルフィ</t>
   </si>
@@ -1246,6 +1246,10 @@
   </si>
   <si>
     <t>F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4662,7 +4666,7 @@
         <v>386</v>
       </c>
       <c r="B381" t="s">
-        <v>3</v>
+        <v>404</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.4">

--- a/data/bloodtype.xlsx
+++ b/data/bloodtype.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E605AB9-02AD-4E4A-9D31-E27DB6801538}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CD8ABB7-6C34-4B90-B0CF-EA1715F4CC91}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="7980" windowHeight="13170" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="7980" windowHeight="13170" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4682,7 +4682,7 @@
         <v>388</v>
       </c>
       <c r="B383" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.4">

--- a/data/bloodtype.xlsx
+++ b/data/bloodtype.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CD8ABB7-6C34-4B90-B0CF-EA1715F4CC91}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{251ACDBA-E000-413C-B896-2CC8A317F440}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="7980" windowHeight="13170" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="11955" windowHeight="13170" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,17 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="405">
-  <si>
-    <t>ルフィ</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="432">
   <si>
     <t>F</t>
   </si>
   <si>
-    <t>ゾロ</t>
-  </si>
-  <si>
     <t>XF</t>
   </si>
   <si>
@@ -54,21 +48,12 @@
     <t>X</t>
   </si>
   <si>
-    <t>ウソップ</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
     <t>サンジ</t>
   </si>
   <si>
-    <t>チョッパー</t>
-  </si>
-  <si>
-    <t>ロビン</t>
-  </si>
-  <si>
     <t>フランキー</t>
   </si>
   <si>
@@ -78,21 +63,12 @@
     <t>ジンベエ</t>
   </si>
   <si>
-    <t>ロジャー</t>
-  </si>
-  <si>
     <t>シャンクス</t>
   </si>
   <si>
-    <t>ルウ</t>
-  </si>
-  <si>
     <t>ヤソップ</t>
   </si>
   <si>
-    <t>ベックマン</t>
-  </si>
-  <si>
     <t>マキノ</t>
   </si>
   <si>
@@ -180,9 +156,6 @@
     <t>クリーク</t>
   </si>
   <si>
-    <t>ミホーク</t>
-  </si>
-  <si>
     <t>パール</t>
   </si>
   <si>
@@ -222,18 +195,12 @@
     <t>たしぎ</t>
   </si>
   <si>
-    <t>ドラゴン</t>
-  </si>
-  <si>
     <t>ラブーン</t>
   </si>
   <si>
     <t>クロッカス</t>
   </si>
   <si>
-    <t>ビビ</t>
-  </si>
-  <si>
     <t>イガラム</t>
   </si>
   <si>
@@ -270,21 +237,12 @@
     <t>ドルトン</t>
   </si>
   <si>
-    <t>くれは</t>
-  </si>
-  <si>
     <t>チェス</t>
   </si>
   <si>
     <t>クロマーリモ</t>
   </si>
   <si>
-    <t>ヒルルク</t>
-  </si>
-  <si>
-    <t>コブラ</t>
-  </si>
-  <si>
     <t>ペル</t>
   </si>
   <si>
@@ -312,12 +270,6 @@
     <t>ドロフィー</t>
   </si>
   <si>
-    <t>ベーブ</t>
-  </si>
-  <si>
-    <t>ザラ</t>
-  </si>
-  <si>
     <t>ダズ・ボーネス</t>
   </si>
   <si>
@@ -342,21 +294,12 @@
     <t>ショウジョウ</t>
   </si>
   <si>
-    <t>クリケット</t>
-  </si>
-  <si>
     <t>ラフィット</t>
   </si>
   <si>
-    <t>バージェス</t>
-  </si>
-  <si>
     <t>ヴァン・オーガー</t>
   </si>
   <si>
-    <t>ティーチ</t>
-  </si>
-  <si>
     <t>ドクQ</t>
   </si>
   <si>
@@ -372,9 +315,6 @@
     <t>パガヤ</t>
   </si>
   <si>
-    <t>ノーランド</t>
-  </si>
-  <si>
     <t>サトリ</t>
   </si>
   <si>
@@ -438,9 +378,6 @@
     <t>パウリー</t>
   </si>
   <si>
-    <t>ルル</t>
-  </si>
-  <si>
     <t>キウイ</t>
   </si>
   <si>
@@ -462,12 +399,6 @@
     <t>クローバー</t>
   </si>
   <si>
-    <t>サウロ</t>
-  </si>
-  <si>
-    <t>オルビア</t>
-  </si>
-  <si>
     <t>カク</t>
   </si>
   <si>
@@ -504,24 +435,12 @@
     <t>クマドリ</t>
   </si>
   <si>
-    <t>アンド</t>
-  </si>
-  <si>
-    <t>バス</t>
-  </si>
-  <si>
-    <t>カビル</t>
-  </si>
-  <si>
     <t>スパンダイン</t>
   </si>
   <si>
     <t>モモンガ</t>
   </si>
   <si>
-    <t>くま</t>
-  </si>
-  <si>
     <t>シンドリー</t>
   </si>
   <si>
@@ -537,18 +456,9 @@
     <t>リューマ</t>
   </si>
   <si>
-    <t>ローラ</t>
-  </si>
-  <si>
     <t>ジゴロウ</t>
   </si>
   <si>
-    <t>モリア</t>
-  </si>
-  <si>
-    <t>オーズ</t>
-  </si>
-  <si>
     <t>ケイミー</t>
   </si>
   <si>
@@ -561,51 +471,21 @@
     <t>シャクヤク</t>
   </si>
   <si>
-    <t>ベッジ</t>
-  </si>
-  <si>
-    <t>ボニー</t>
-  </si>
-  <si>
-    <t>ホーキンス</t>
-  </si>
-  <si>
-    <t>キッド</t>
-  </si>
-  <si>
-    <t>アプー</t>
-  </si>
-  <si>
-    <t>ドレーク</t>
-  </si>
-  <si>
     <t>ウルージ</t>
   </si>
   <si>
     <t>キラー</t>
   </si>
   <si>
-    <t>ロー</t>
-  </si>
-  <si>
     <t>ベポ</t>
   </si>
   <si>
-    <t>レイリー</t>
-  </si>
-  <si>
     <t>ハレダス</t>
   </si>
   <si>
     <t>ヘラクレス</t>
   </si>
   <si>
-    <t>エース</t>
-  </si>
-  <si>
-    <t>白ひげ</t>
-  </si>
-  <si>
     <t>マルコ</t>
   </si>
   <si>
@@ -615,15 +495,6 @@
     <t>マーガレット</t>
   </si>
   <si>
-    <t>ハンコック</t>
-  </si>
-  <si>
-    <t>サンダーソニア</t>
-  </si>
-  <si>
-    <t>マリーゴールド</t>
-  </si>
-  <si>
     <t>ボルサリーノ</t>
   </si>
   <si>
@@ -645,9 +516,6 @@
     <t>イナズマ</t>
   </si>
   <si>
-    <t>イワンコフ</t>
-  </si>
-  <si>
     <t>シリュウ</t>
   </si>
   <si>
@@ -711,12 +579,6 @@
     <t>ドリップ</t>
   </si>
   <si>
-    <t>のらギツネ</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>カリブー</t>
   </si>
   <si>
@@ -771,9 +633,6 @@
     <t>ヒョウゾウ</t>
   </si>
   <si>
-    <t>ホーディ</t>
-  </si>
-  <si>
     <t>ドスン</t>
   </si>
   <si>
@@ -810,9 +669,6 @@
     <t>モネ</t>
   </si>
   <si>
-    <t>シーザー</t>
-  </si>
-  <si>
     <t>ロック</t>
   </si>
   <si>
@@ -828,9 +684,6 @@
     <t>光月モモの助</t>
   </si>
   <si>
-    <t>ベビー５</t>
-  </si>
-  <si>
     <t>バッファロー</t>
   </si>
   <si>
@@ -873,18 +726,12 @@
     <t>ブルーギリー</t>
   </si>
   <si>
-    <t>リク・ドルド３世</t>
-  </si>
-  <si>
     <t>レオ</t>
   </si>
   <si>
     <t>マンシェリー</t>
   </si>
   <si>
-    <t>ドフラミンゴ</t>
-  </si>
-  <si>
     <t>ヴィオラ</t>
   </si>
   <si>
@@ -903,9 +750,6 @@
     <t>シュガー</t>
   </si>
   <si>
-    <t>セニョール</t>
-  </si>
-  <si>
     <t>マッハバイス</t>
   </si>
   <si>
@@ -921,21 +765,12 @@
     <t>ピーカ</t>
   </si>
   <si>
-    <t>カン十郎</t>
-  </si>
-  <si>
-    <t>ロシナンテ</t>
-  </si>
-  <si>
     <t>ハック</t>
   </si>
   <si>
     <t>バスティーユ</t>
   </si>
   <si>
-    <t>ウィーブル</t>
-  </si>
-  <si>
     <t>バッキン</t>
   </si>
   <si>
@@ -975,30 +810,9 @@
     <t>ゴッティ</t>
   </si>
   <si>
-    <t>ヨンジ</t>
-  </si>
-  <si>
-    <t>レイジュ</t>
-  </si>
-  <si>
-    <t>プラリネ</t>
-  </si>
-  <si>
     <t>パウンド</t>
   </si>
   <si>
-    <t>ジャッジ</t>
-  </si>
-  <si>
-    <t>シフォン</t>
-  </si>
-  <si>
-    <t>イチジ</t>
-  </si>
-  <si>
-    <t>ニジ</t>
-  </si>
-  <si>
     <t>モルガンズ</t>
   </si>
   <si>
@@ -1011,45 +825,12 @@
     <t>ヤルル</t>
   </si>
   <si>
-    <t>プリン</t>
-  </si>
-  <si>
-    <t>リンリン</t>
-  </si>
-  <si>
-    <t>ブリュレ</t>
-  </si>
-  <si>
-    <t>ペロスペロー</t>
-  </si>
-  <si>
-    <t>クラッカー</t>
-  </si>
-  <si>
-    <t>モンドール</t>
-  </si>
-  <si>
-    <t>スムージー</t>
-  </si>
-  <si>
     <t>シュトロイゼン</t>
   </si>
   <si>
-    <t>カタクリ</t>
-  </si>
-  <si>
-    <t>ダイフク</t>
-  </si>
-  <si>
-    <t>オーブン</t>
-  </si>
-  <si>
     <t>カルメル</t>
   </si>
   <si>
-    <t>フランペ</t>
-  </si>
-  <si>
     <t>つる</t>
   </si>
   <si>
@@ -1059,9 +840,6 @@
     <t>クザン</t>
   </si>
   <si>
-    <t>ガープ</t>
-  </si>
-  <si>
     <t>シャルリア宮</t>
   </si>
   <si>
@@ -1080,9 +858,6 @@
     <t>お玉</t>
   </si>
   <si>
-    <t>お菊</t>
-  </si>
-  <si>
     <t>霜月康イエ</t>
   </si>
   <si>
@@ -1122,9 +897,6 @@
     <t>河松</t>
   </si>
   <si>
-    <t>お鶴（鶴女）</t>
-  </si>
-  <si>
     <t>しのぶ</t>
   </si>
   <si>
@@ -1134,12 +906,6 @@
     <t>光月日和</t>
   </si>
   <si>
-    <t>天狗山飛徹</t>
-  </si>
-  <si>
-    <t>オロチ</t>
-  </si>
-  <si>
     <t>福ロクジュ</t>
   </si>
   <si>
@@ -1173,9 +939,6 @@
     <t>ビシャ門</t>
   </si>
   <si>
-    <t>オニ丸（牛鬼丸）</t>
-  </si>
-  <si>
     <t>カイドウ</t>
   </si>
   <si>
@@ -1234,9 +997,6 @@
   </si>
   <si>
     <t>ベガパンク</t>
-  </si>
-  <si>
-    <t>孔雀</t>
   </si>
   <si>
     <t>ジニー</t>
@@ -1250,6 +1010,386 @@
   </si>
   <si>
     <t>S</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>XF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンキー・D・ルフィ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンキー・D・ルフィ(7歳）</t>
+    <rPh sb="12" eb="13">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロロノア・ゾロ</t>
+  </si>
+  <si>
+    <t>ウソップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トニートニー・チョッパー</t>
+  </si>
+  <si>
+    <t>ニコ・ロビン</t>
+  </si>
+  <si>
+    <t>ネフェルタリ・ビビ</t>
+  </si>
+  <si>
+    <t>ゴール・D・ロジャー</t>
+  </si>
+  <si>
+    <t>シャンクス（13歳）</t>
+    <rPh sb="8" eb="9">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラッキー・ルウ</t>
+  </si>
+  <si>
+    <t>ベン・ベックマン</t>
+  </si>
+  <si>
+    <t>バギー（13歳）</t>
+    <rPh sb="6" eb="7">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モージ（リッチー搭乗時）</t>
+    <rPh sb="8" eb="10">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジュラキュール・ミホーク</t>
+  </si>
+  <si>
+    <t>モンキー・D・ドラゴン</t>
+  </si>
+  <si>
+    <t>Dr.くれは</t>
+  </si>
+  <si>
+    <t>Dr.ヒルルク</t>
+  </si>
+  <si>
+    <t>ネフェルタリ・コブラ</t>
+  </si>
+  <si>
+    <t>ポートガス・D・エース(10歳）</t>
+    <rPh sb="14" eb="15">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポートガス・D・エース</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ベーブ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ザラ </t>
+  </si>
+  <si>
+    <t>モンブラン・クリケット</t>
+  </si>
+  <si>
+    <t>ドンキホーテ・ドフラミンゴ</t>
+  </si>
+  <si>
+    <t>バーソロミュー・くま</t>
+  </si>
+  <si>
+    <t>エドワード・ニューゲート</t>
+  </si>
+  <si>
+    <t>ジーザス・バージェス</t>
+  </si>
+  <si>
+    <t>マーシャル・D・ティーチ</t>
+  </si>
+  <si>
+    <t>ホトリ</t>
+  </si>
+  <si>
+    <t>コトリ</t>
+  </si>
+  <si>
+    <t>モンブラン・ノーランド</t>
+  </si>
+  <si>
+    <t>ピープリ―・ルル</t>
+  </si>
+  <si>
+    <t>バス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カビル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハグワール・D・サウロ</t>
+  </si>
+  <si>
+    <t>ニコ・オルビア</t>
+  </si>
+  <si>
+    <t>モンキー・D・ガープ</t>
+  </si>
+  <si>
+    <t>シャーロット・ローラ</t>
+  </si>
+  <si>
+    <t>ゲッコー・モリア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オーズ </t>
+  </si>
+  <si>
+    <t>カポネ・ベッジ</t>
+  </si>
+  <si>
+    <t>ジュエリー・ボニー(見た目）</t>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジュエリー・ボニー</t>
+  </si>
+  <si>
+    <t>バジル・ホーキンス</t>
+  </si>
+  <si>
+    <t>ユースタス・キッド</t>
+  </si>
+  <si>
+    <t>スクラッチメン・アプー</t>
+  </si>
+  <si>
+    <t>X・ドレーク</t>
+  </si>
+  <si>
+    <t>トラファルガー・ロー</t>
+  </si>
+  <si>
+    <t>シルバーズ・レイリー</t>
+  </si>
+  <si>
+    <t>ボア・ハンコック</t>
+  </si>
+  <si>
+    <t>ボア・サンダーソニア</t>
+  </si>
+  <si>
+    <t>ボア・マリーゴールド</t>
+  </si>
+  <si>
+    <t>エンポリオ・イワンコフ</t>
+  </si>
+  <si>
+    <t>サボ（10歳）</t>
+    <rPh sb="5" eb="6">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホーディ・ジョーンズ</t>
+  </si>
+  <si>
+    <t>ドンキホーテ・ミョスガルド聖</t>
+  </si>
+  <si>
+    <t>シーザー・クラウン</t>
+  </si>
+  <si>
+    <t>光月モモの助（未来の姿）</t>
+    <rPh sb="7" eb="9">
+      <t>ミライ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>スガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベビー5</t>
+  </si>
+  <si>
+    <t>ゲルニカ</t>
+  </si>
+  <si>
+    <t>リク・ドルド3世</t>
+  </si>
+  <si>
+    <t>セニョール・ピンク</t>
+  </si>
+  <si>
+    <t>黒炭カン十郎</t>
+  </si>
+  <si>
+    <t>ドンキホーテ・ロシナンテ</t>
+  </si>
+  <si>
+    <t>エドワード・ウィーブル</t>
+  </si>
+  <si>
+    <t>シャーロット・プリン</t>
+  </si>
+  <si>
+    <t>ヴィンスモーク・ヨンジ</t>
+  </si>
+  <si>
+    <t>ヴィンスモーク・レイジュ</t>
+  </si>
+  <si>
+    <t>シャーロット・リンリン</t>
+  </si>
+  <si>
+    <t>シャーロット・プラリネ</t>
+  </si>
+  <si>
+    <t>シャーロット・ブリュレ</t>
+  </si>
+  <si>
+    <t>ヴィンスモーク・ジャッジ</t>
+  </si>
+  <si>
+    <t>シャーロット・シフォン</t>
+  </si>
+  <si>
+    <t>シャーロット・ペロスペロー</t>
+  </si>
+  <si>
+    <t>シャーロット・クラッカー</t>
+  </si>
+  <si>
+    <t>ヴィンスモーク・イチジ</t>
+  </si>
+  <si>
+    <t>S型RH-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヴィンスモーク・ニジ</t>
+  </si>
+  <si>
+    <t>シャーロット・モンドール</t>
+  </si>
+  <si>
+    <t>シャーロット・スムージー</t>
+  </si>
+  <si>
+    <t>シャーロット・カタクリ</t>
+  </si>
+  <si>
+    <t>シャーロット・ダイフク</t>
+  </si>
+  <si>
+    <t>シャーロット・オーブン</t>
+  </si>
+  <si>
+    <t>シャーロット・フランペ</t>
+  </si>
+  <si>
+    <t>光月スキヤキ</t>
+  </si>
+  <si>
+    <t>お鶴</t>
+  </si>
+  <si>
+    <t>菊之丞</t>
+  </si>
+  <si>
+    <t>黒炭オロチ</t>
+  </si>
+  <si>
+    <t>オニ丸 (牛鬼丸)</t>
+  </si>
+  <si>
+    <t>霜月牛マル</t>
+  </si>
+  <si>
+    <t>霜月コウ三郎</t>
+  </si>
+  <si>
+    <t>黒炭ひぐらし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒炭せみ丸</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒炭せみ丸（胡坐時）</t>
+    <rPh sb="6" eb="9">
+      <t>アグラジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雨月天ぷら</t>
+  </si>
+  <si>
+    <t>風月おむすび</t>
+  </si>
+  <si>
+    <t>二牙</t>
+  </si>
+  <si>
+    <t>アラマキ</t>
+  </si>
+  <si>
+    <t>正</t>
+  </si>
+  <si>
+    <t>暴</t>
+  </si>
+  <si>
+    <t>想</t>
+  </si>
+  <si>
+    <t>知</t>
+  </si>
+  <si>
+    <t>欲</t>
+  </si>
+  <si>
+    <t>孔雀</t>
+    <rPh sb="0" eb="2">
+      <t>クジャク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1618,2076 +1758,2079 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11175D96-3E6B-485A-87F0-242E058A062D}">
-  <dimension ref="A1:B397"/>
+  <dimension ref="A1:B422"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="29.625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>328</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>333</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>336</v>
       </c>
       <c r="B5" t="s">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>338</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>343</v>
       </c>
       <c r="B24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>344</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>347</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="B33" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>266</v>
       </c>
       <c r="B37" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>352</v>
       </c>
       <c r="B38" t="s">
-        <v>1</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>353</v>
       </c>
       <c r="B39" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="B44" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="B46" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>267</v>
       </c>
       <c r="B47" t="s">
-        <v>3</v>
+        <v>323</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="B48" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="B49" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="B50" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="B51" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="B52" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>362</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>364</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="B57" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="B58" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>365</v>
       </c>
       <c r="B59" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>367</v>
       </c>
       <c r="B60" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>369</v>
       </c>
       <c r="B61" t="s">
-        <v>3</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>370</v>
       </c>
       <c r="B62" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>372</v>
       </c>
       <c r="B63" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>375</v>
       </c>
       <c r="B64" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>154</v>
       </c>
       <c r="B65" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="B66" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="B67" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>157</v>
       </c>
       <c r="B68" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="B69" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="B70" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="B71" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="B72" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="B73" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>382</v>
       </c>
       <c r="B74" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="B75" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="B76" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="B77" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>216</v>
       </c>
       <c r="B78" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="B79" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="B80" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>221</v>
       </c>
       <c r="B81" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>387</v>
       </c>
       <c r="B82" t="s">
-        <v>5</v>
+        <v>323</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>243</v>
       </c>
       <c r="B83" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>244</v>
       </c>
       <c r="B84" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>239</v>
       </c>
       <c r="B85" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>241</v>
       </c>
       <c r="B86" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>246</v>
       </c>
       <c r="B87" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>247</v>
       </c>
       <c r="B88" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>248</v>
       </c>
       <c r="B89" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>249</v>
       </c>
       <c r="B90" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>251</v>
       </c>
       <c r="B91" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>256</v>
       </c>
       <c r="B92" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>395</v>
       </c>
       <c r="B93" t="s">
-        <v>5</v>
+        <v>323</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="B94" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>400</v>
       </c>
       <c r="B95" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>99</v>
+        <v>407</v>
       </c>
       <c r="B96" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>410</v>
       </c>
       <c r="B97" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>101</v>
+        <v>261</v>
       </c>
       <c r="B98" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="B99" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="B100" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>278</v>
       </c>
       <c r="B101" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>105</v>
+        <v>273</v>
       </c>
       <c r="B102" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>106</v>
+        <v>412</v>
       </c>
       <c r="B103" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>413</v>
       </c>
       <c r="B104" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>312</v>
       </c>
       <c r="B105" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>109</v>
+        <v>287</v>
       </c>
       <c r="B106" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="B107" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>111</v>
+        <v>274</v>
       </c>
       <c r="B108" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>112</v>
+        <v>292</v>
       </c>
       <c r="B109" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>113</v>
+        <v>295</v>
       </c>
       <c r="B110" t="s">
-        <v>7</v>
+        <v>323</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>114</v>
+        <v>297</v>
       </c>
       <c r="B111" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>115</v>
+        <v>298</v>
       </c>
       <c r="B112" t="s">
-        <v>1</v>
+        <v>323</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>116</v>
+        <v>286</v>
       </c>
       <c r="B113" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>280</v>
       </c>
       <c r="B114" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>118</v>
+        <v>419</v>
       </c>
       <c r="B115" t="s">
-        <v>7</v>
+        <v>323</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>119</v>
+        <v>420</v>
       </c>
       <c r="B116" t="s">
-        <v>5</v>
+        <v>323</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>120</v>
+        <v>421</v>
       </c>
       <c r="B117" t="s">
-        <v>7</v>
+        <v>323</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>121</v>
+        <v>306</v>
       </c>
       <c r="B118" t="s">
-        <v>3</v>
+        <v>323</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>122</v>
+        <v>310</v>
       </c>
       <c r="B119" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>315</v>
       </c>
       <c r="B120" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>124</v>
+        <v>319</v>
       </c>
       <c r="B121" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>125</v>
+        <v>321</v>
       </c>
       <c r="B122" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="B123" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>127</v>
+        <v>332</v>
       </c>
       <c r="B124" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>128</v>
+        <v>334</v>
       </c>
       <c r="B125" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="B126" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="B128" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="B131" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>136</v>
+        <v>339</v>
       </c>
       <c r="B133" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>137</v>
+        <v>26</v>
       </c>
       <c r="B134" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
       <c r="B135" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="B136" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>140</v>
+        <v>38</v>
       </c>
       <c r="B137" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>141</v>
+        <v>340</v>
       </c>
       <c r="B138" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>142</v>
+        <v>47</v>
       </c>
       <c r="B139" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="B140" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="B141" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="B142" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>146</v>
+        <v>52</v>
       </c>
       <c r="B143" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>147</v>
+        <v>342</v>
       </c>
       <c r="B144" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>148</v>
+        <v>67</v>
       </c>
       <c r="B145" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="B146" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>150</v>
+        <v>345</v>
       </c>
       <c r="B147" t="s">
-        <v>5</v>
+        <v>324</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>151</v>
+        <v>346</v>
       </c>
       <c r="B148" t="s">
-        <v>1</v>
+        <v>324</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="B149" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="B150" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>154</v>
+        <v>57</v>
       </c>
       <c r="B151" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>155</v>
+        <v>62</v>
       </c>
       <c r="B152" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>156</v>
+        <v>349</v>
       </c>
       <c r="B153" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="B154" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="B155" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
       <c r="B156" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="B157" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="B158" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="B159" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="B160" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>164</v>
+        <v>355</v>
       </c>
       <c r="B161" t="s">
-        <v>1</v>
+        <v>324</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>165</v>
+        <v>356</v>
       </c>
       <c r="B162" t="s">
-        <v>3</v>
+        <v>324</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>166</v>
+        <v>357</v>
       </c>
       <c r="B163" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="B164" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="B165" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="B166" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="B167" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="B168" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>172</v>
+        <v>358</v>
       </c>
       <c r="B169" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="B170" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="B171" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="B172" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
-        <v>176</v>
+        <v>363</v>
       </c>
       <c r="B173" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="B174" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="B175" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>179</v>
+        <v>368</v>
       </c>
       <c r="B176" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>180</v>
+        <v>371</v>
       </c>
       <c r="B177" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="B178" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="B179" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>183</v>
+        <v>377</v>
       </c>
       <c r="B180" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>184</v>
+        <v>378</v>
       </c>
       <c r="B181" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>185</v>
+        <v>379</v>
       </c>
       <c r="B182" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="B183" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="B184" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="B185" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="B186" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B187" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="B188" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="B189" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B190" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B191" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B192" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B193" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B196" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B197" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>201</v>
+        <v>271</v>
       </c>
       <c r="B198" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="B199" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="B200" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="B201" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="B202" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>206</v>
+        <v>388</v>
       </c>
       <c r="B203" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="B204" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="B205" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="B206" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="B207" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>211</v>
+        <v>391</v>
       </c>
       <c r="B208" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>212</v>
+        <v>301</v>
       </c>
       <c r="B209" t="s">
-        <v>1</v>
+        <v>324</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>213</v>
+        <v>392</v>
       </c>
       <c r="B210" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="B211" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="B212" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="B213" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="B214" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="B215" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>219</v>
+        <v>398</v>
       </c>
       <c r="B216" t="s">
-        <v>5</v>
+        <v>324</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
-        <v>220</v>
+        <v>399</v>
       </c>
       <c r="B217" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
-        <v>221</v>
+        <v>272</v>
       </c>
       <c r="B218" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="B219" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="B220" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="B221" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>225</v>
+        <v>411</v>
       </c>
       <c r="B222" t="s">
-        <v>226</v>
+        <v>4</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="B223" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B224" t="s">
-        <v>3</v>
+        <v>324</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>229</v>
+        <v>288</v>
       </c>
       <c r="B225" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>230</v>
+        <v>293</v>
       </c>
       <c r="B226" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
-        <v>231</v>
+        <v>299</v>
       </c>
       <c r="B227" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>232</v>
+        <v>307</v>
       </c>
       <c r="B228" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>233</v>
+        <v>423</v>
       </c>
       <c r="B229" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>234</v>
+        <v>424</v>
       </c>
       <c r="B230" t="s">
-        <v>5</v>
+        <v>324</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>235</v>
+        <v>313</v>
       </c>
       <c r="B231" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>236</v>
+        <v>314</v>
       </c>
       <c r="B232" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>237</v>
+        <v>317</v>
       </c>
       <c r="B233" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>238</v>
+        <v>426</v>
       </c>
       <c r="B234" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>239</v>
+        <v>427</v>
       </c>
       <c r="B235" t="s">
-        <v>240</v>
+        <v>4</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>241</v>
+        <v>428</v>
       </c>
       <c r="B236" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>242</v>
+        <v>429</v>
       </c>
       <c r="B237" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>243</v>
+        <v>430</v>
       </c>
       <c r="B238" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>244</v>
+        <v>320</v>
       </c>
       <c r="B239" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
-        <v>245</v>
+        <v>5</v>
       </c>
       <c r="B240" t="s">
-        <v>1</v>
+        <v>194</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="B241" t="s">
-        <v>7</v>
+        <v>194</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="B242" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="B243" t="s">
-        <v>1</v>
+        <v>194</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="B244" t="s">
-        <v>3</v>
+        <v>194</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>250</v>
+        <v>394</v>
       </c>
       <c r="B245" t="s">
-        <v>1</v>
+        <v>194</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>251</v>
+        <v>397</v>
       </c>
       <c r="B246" t="s">
-        <v>3</v>
+        <v>194</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>252</v>
+        <v>403</v>
       </c>
       <c r="B247" t="s">
-        <v>7</v>
+        <v>404</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>253</v>
+        <v>405</v>
       </c>
       <c r="B248" t="s">
-        <v>3</v>
+        <v>194</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
-        <v>254</v>
+        <v>2</v>
       </c>
       <c r="B249" t="s">
-        <v>5</v>
+        <v>325</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A250" t="s">
-        <v>255</v>
+        <v>331</v>
       </c>
       <c r="B250" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>256</v>
+        <v>7</v>
       </c>
       <c r="B251" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>257</v>
+        <v>337</v>
       </c>
       <c r="B252" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
-        <v>258</v>
+        <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
-        <v>259</v>
+        <v>22</v>
       </c>
       <c r="B254" t="s">
-        <v>240</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
-        <v>260</v>
+        <v>23</v>
       </c>
       <c r="B255" t="s">
-        <v>240</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
-        <v>261</v>
+        <v>25</v>
       </c>
       <c r="B256" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="B257" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
-        <v>263</v>
+        <v>30</v>
       </c>
       <c r="B258" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
-        <v>264</v>
+        <v>31</v>
       </c>
       <c r="B259" t="s">
         <v>3</v>
@@ -3695,71 +3838,71 @@
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
-        <v>265</v>
+        <v>36</v>
       </c>
       <c r="B260" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
-        <v>266</v>
+        <v>45</v>
       </c>
       <c r="B261" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="B262" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
-        <v>268</v>
+        <v>50</v>
       </c>
       <c r="B263" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>269</v>
+        <v>55</v>
       </c>
       <c r="B264" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
-        <v>270</v>
+        <v>71</v>
       </c>
       <c r="B265" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>271</v>
+        <v>65</v>
       </c>
       <c r="B266" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
-        <v>272</v>
+        <v>66</v>
       </c>
       <c r="B267" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
-        <v>273</v>
+        <v>348</v>
       </c>
       <c r="B268" t="s">
         <v>3</v>
@@ -3767,31 +3910,31 @@
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A269" t="s">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="B269" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A270" t="s">
-        <v>275</v>
+        <v>69</v>
       </c>
       <c r="B270" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A271" t="s">
-        <v>276</v>
+        <v>58</v>
       </c>
       <c r="B271" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A272" t="s">
-        <v>277</v>
+        <v>85</v>
       </c>
       <c r="B272" t="s">
         <v>3</v>
@@ -3799,71 +3942,71 @@
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="B273" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
-        <v>279</v>
+        <v>350</v>
       </c>
       <c r="B274" t="s">
-        <v>7</v>
+        <v>325</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
-        <v>280</v>
+        <v>351</v>
       </c>
       <c r="B275" t="s">
-        <v>7</v>
+        <v>325</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A276" t="s">
-        <v>281</v>
+        <v>86</v>
       </c>
       <c r="B276" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A277" t="s">
-        <v>282</v>
+        <v>87</v>
       </c>
       <c r="B277" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A278" t="s">
-        <v>283</v>
+        <v>89</v>
       </c>
       <c r="B278" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
-        <v>284</v>
+        <v>90</v>
       </c>
       <c r="B279" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A280" t="s">
-        <v>285</v>
+        <v>97</v>
       </c>
       <c r="B280" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
-        <v>286</v>
+        <v>99</v>
       </c>
       <c r="B281" t="s">
         <v>3</v>
@@ -3871,15 +4014,15 @@
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A282" t="s">
-        <v>287</v>
+        <v>105</v>
       </c>
       <c r="B282" t="s">
-        <v>240</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
-        <v>288</v>
+        <v>106</v>
       </c>
       <c r="B283" t="s">
         <v>3</v>
@@ -3887,135 +4030,135 @@
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A284" t="s">
-        <v>289</v>
+        <v>121</v>
       </c>
       <c r="B284" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
-        <v>290</v>
+        <v>112</v>
       </c>
       <c r="B285" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A286" t="s">
-        <v>291</v>
+        <v>124</v>
       </c>
       <c r="B286" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A287" t="s">
-        <v>292</v>
+        <v>127</v>
       </c>
       <c r="B287" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A288" t="s">
-        <v>293</v>
+        <v>129</v>
       </c>
       <c r="B288" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A289" t="s">
-        <v>294</v>
+        <v>118</v>
       </c>
       <c r="B289" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="B290" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A291" t="s">
-        <v>296</v>
+        <v>120</v>
       </c>
       <c r="B291" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
-        <v>297</v>
+        <v>150</v>
       </c>
       <c r="B292" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A293" t="s">
-        <v>298</v>
+        <v>151</v>
       </c>
       <c r="B293" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
-        <v>299</v>
+        <v>366</v>
       </c>
       <c r="B294" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A295" t="s">
-        <v>300</v>
+        <v>141</v>
       </c>
       <c r="B295" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A296" t="s">
-        <v>301</v>
+        <v>144</v>
       </c>
       <c r="B296" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="B297" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A298" t="s">
-        <v>303</v>
+        <v>146</v>
       </c>
       <c r="B298" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A299" t="s">
-        <v>304</v>
+        <v>148</v>
       </c>
       <c r="B299" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
-        <v>305</v>
+        <v>156</v>
       </c>
       <c r="B300" t="s">
         <v>3</v>
@@ -4023,127 +4166,127 @@
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A301" t="s">
-        <v>306</v>
+        <v>160</v>
       </c>
       <c r="B301" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A302" t="s">
-        <v>307</v>
+        <v>166</v>
       </c>
       <c r="B302" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="B303" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A304" t="s">
-        <v>309</v>
+        <v>162</v>
       </c>
       <c r="B304" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A305" t="s">
-        <v>310</v>
+        <v>164</v>
       </c>
       <c r="B305" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A306" t="s">
-        <v>311</v>
+        <v>169</v>
       </c>
       <c r="B306" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A307" t="s">
-        <v>312</v>
+        <v>170</v>
       </c>
       <c r="B307" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A308" t="s">
-        <v>313</v>
+        <v>381</v>
       </c>
       <c r="B308" t="s">
-        <v>240</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A309" t="s">
-        <v>314</v>
+        <v>172</v>
       </c>
       <c r="B309" t="s">
-        <v>403</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A310" t="s">
-        <v>315</v>
+        <v>173</v>
       </c>
       <c r="B310" t="s">
-        <v>240</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A311" t="s">
-        <v>316</v>
+        <v>176</v>
       </c>
       <c r="B311" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
-        <v>317</v>
+        <v>175</v>
       </c>
       <c r="B312" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A313" t="s">
-        <v>318</v>
+        <v>179</v>
       </c>
       <c r="B313" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A314" t="s">
-        <v>319</v>
+        <v>198</v>
       </c>
       <c r="B314" t="s">
-        <v>240</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A315" t="s">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="B315" t="s">
-        <v>240</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A316" t="s">
-        <v>321</v>
+        <v>188</v>
       </c>
       <c r="B316" t="s">
         <v>3</v>
@@ -4151,95 +4294,95 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A317" t="s">
-        <v>322</v>
+        <v>190</v>
       </c>
       <c r="B317" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A318" t="s">
-        <v>323</v>
+        <v>191</v>
       </c>
       <c r="B318" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A319" t="s">
-        <v>324</v>
+        <v>192</v>
       </c>
       <c r="B319" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A320" t="s">
+        <v>383</v>
+      </c>
+      <c r="B320" t="s">
         <v>325</v>
-      </c>
-      <c r="B320" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
-        <v>326</v>
+        <v>210</v>
       </c>
       <c r="B321" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A322" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="B322" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A323" t="s">
-        <v>328</v>
+        <v>213</v>
       </c>
       <c r="B323" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A324" t="s">
-        <v>329</v>
+        <v>214</v>
       </c>
       <c r="B324" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
-        <v>330</v>
+        <v>385</v>
       </c>
       <c r="B325" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A326" t="s">
-        <v>331</v>
+        <v>215</v>
       </c>
       <c r="B326" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A327" t="s">
-        <v>332</v>
+        <v>232</v>
       </c>
       <c r="B327" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A328" t="s">
-        <v>333</v>
+        <v>219</v>
       </c>
       <c r="B328" t="s">
         <v>3</v>
@@ -4247,71 +4390,71 @@
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A329" t="s">
-        <v>334</v>
+        <v>220</v>
       </c>
       <c r="B329" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A330" t="s">
-        <v>335</v>
+        <v>223</v>
       </c>
       <c r="B330" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A331" t="s">
-        <v>336</v>
+        <v>226</v>
       </c>
       <c r="B331" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A332" t="s">
-        <v>337</v>
+        <v>227</v>
       </c>
       <c r="B332" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
-        <v>338</v>
+        <v>389</v>
       </c>
       <c r="B333" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A334" t="s">
-        <v>339</v>
+        <v>242</v>
       </c>
       <c r="B334" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A335" t="s">
-        <v>340</v>
+        <v>390</v>
       </c>
       <c r="B335" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A336" t="s">
-        <v>341</v>
+        <v>231</v>
       </c>
       <c r="B336" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A337" t="s">
-        <v>342</v>
+        <v>253</v>
       </c>
       <c r="B337" t="s">
         <v>3</v>
@@ -4319,7 +4462,7 @@
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A338" t="s">
-        <v>343</v>
+        <v>283</v>
       </c>
       <c r="B338" t="s">
         <v>3</v>
@@ -4327,7 +4470,7 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A339" t="s">
-        <v>344</v>
+        <v>396</v>
       </c>
       <c r="B339" t="s">
         <v>3</v>
@@ -4335,31 +4478,31 @@
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A340" t="s">
-        <v>345</v>
+        <v>401</v>
       </c>
       <c r="B340" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A341" t="s">
-        <v>346</v>
+        <v>402</v>
       </c>
       <c r="B341" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A342" t="s">
-        <v>347</v>
+        <v>406</v>
       </c>
       <c r="B342" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A343" t="s">
-        <v>348</v>
+        <v>409</v>
       </c>
       <c r="B343" t="s">
         <v>3</v>
@@ -4367,31 +4510,31 @@
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A344" t="s">
-        <v>349</v>
+        <v>311</v>
       </c>
       <c r="B344" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A345" t="s">
-        <v>350</v>
+        <v>285</v>
       </c>
       <c r="B345" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A346" t="s">
-        <v>351</v>
+        <v>304</v>
       </c>
       <c r="B346" t="s">
-        <v>1</v>
+        <v>325</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A347" t="s">
-        <v>352</v>
+        <v>291</v>
       </c>
       <c r="B347" t="s">
         <v>3</v>
@@ -4399,55 +4542,55 @@
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A348" t="s">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="B348" t="s">
-        <v>1</v>
+        <v>325</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A349" t="s">
-        <v>354</v>
+        <v>296</v>
       </c>
       <c r="B349" t="s">
-        <v>7</v>
+        <v>325</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A350" t="s">
-        <v>355</v>
+        <v>290</v>
       </c>
       <c r="B350" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A351" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="B351" t="s">
-        <v>5</v>
+        <v>325</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A352" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="B352" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A353" t="s">
-        <v>358</v>
+        <v>422</v>
       </c>
       <c r="B353" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A354" t="s">
-        <v>359</v>
+        <v>425</v>
       </c>
       <c r="B354" t="s">
         <v>3</v>
@@ -4455,55 +4598,55 @@
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A355" t="s">
-        <v>360</v>
+        <v>316</v>
       </c>
       <c r="B355" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A356" t="s">
-        <v>361</v>
+        <v>318</v>
       </c>
       <c r="B356" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A357" t="s">
-        <v>362</v>
+        <v>431</v>
       </c>
       <c r="B357" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A358" t="s">
-        <v>363</v>
+        <v>329</v>
       </c>
       <c r="B358" t="s">
-        <v>1</v>
+        <v>326</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A359" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="B359" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A360" t="s">
-        <v>365</v>
+        <v>335</v>
       </c>
       <c r="B360" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A361" t="s">
-        <v>366</v>
+        <v>9</v>
       </c>
       <c r="B361" t="s">
         <v>1</v>
@@ -4511,31 +4654,31 @@
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A362" t="s">
-        <v>367</v>
+        <v>16</v>
       </c>
       <c r="B362" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A363" t="s">
-        <v>368</v>
+        <v>24</v>
       </c>
       <c r="B363" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A364" t="s">
-        <v>369</v>
+        <v>35</v>
       </c>
       <c r="B364" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A365" t="s">
-        <v>370</v>
+        <v>39</v>
       </c>
       <c r="B365" t="s">
         <v>1</v>
@@ -4543,15 +4686,15 @@
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A366" t="s">
-        <v>371</v>
+        <v>41</v>
       </c>
       <c r="B366" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A367" t="s">
-        <v>372</v>
+        <v>46</v>
       </c>
       <c r="B367" t="s">
         <v>1</v>
@@ -4559,15 +4702,15 @@
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A368" t="s">
-        <v>373</v>
+        <v>51</v>
       </c>
       <c r="B368" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A369" t="s">
-        <v>374</v>
+        <v>54</v>
       </c>
       <c r="B369" t="s">
         <v>1</v>
@@ -4575,7 +4718,7 @@
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A370" t="s">
-        <v>375</v>
+        <v>72</v>
       </c>
       <c r="B370" t="s">
         <v>1</v>
@@ -4583,31 +4726,31 @@
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A371" t="s">
-        <v>376</v>
+        <v>74</v>
       </c>
       <c r="B371" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A372" t="s">
-        <v>377</v>
+        <v>101</v>
       </c>
       <c r="B372" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A373" t="s">
-        <v>378</v>
+        <v>122</v>
       </c>
       <c r="B373" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A374" t="s">
-        <v>379</v>
+        <v>123</v>
       </c>
       <c r="B374" t="s">
         <v>1</v>
@@ -4615,79 +4758,79 @@
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A375" t="s">
-        <v>380</v>
+        <v>125</v>
       </c>
       <c r="B375" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A376" t="s">
-        <v>381</v>
+        <v>126</v>
       </c>
       <c r="B376" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A377" t="s">
-        <v>382</v>
+        <v>132</v>
       </c>
       <c r="B377" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A378" t="s">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="B378" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A379" t="s">
-        <v>384</v>
+        <v>133</v>
       </c>
       <c r="B379" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A380" t="s">
-        <v>385</v>
+        <v>136</v>
       </c>
       <c r="B380" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A381" t="s">
-        <v>386</v>
+        <v>138</v>
       </c>
       <c r="B381" t="s">
-        <v>404</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A382" t="s">
-        <v>387</v>
+        <v>139</v>
       </c>
       <c r="B382" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A383" t="s">
-        <v>388</v>
+        <v>142</v>
       </c>
       <c r="B383" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A384" t="s">
-        <v>389</v>
+        <v>268</v>
       </c>
       <c r="B384" t="s">
         <v>1</v>
@@ -4695,15 +4838,15 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A385" t="s">
-        <v>390</v>
+        <v>269</v>
       </c>
       <c r="B385" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A386" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="B386" t="s">
         <v>1</v>
@@ -4711,23 +4854,23 @@
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A387" t="s">
-        <v>392</v>
+        <v>270</v>
       </c>
       <c r="B387" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A388" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="B388" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A389" t="s">
-        <v>394</v>
+        <v>153</v>
       </c>
       <c r="B389" t="s">
         <v>1</v>
@@ -4735,31 +4878,31 @@
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A390" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="B390" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A391" t="s">
-        <v>396</v>
+        <v>177</v>
       </c>
       <c r="B391" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A392" t="s">
-        <v>397</v>
+        <v>180</v>
       </c>
       <c r="B392" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A393" t="s">
-        <v>398</v>
+        <v>181</v>
       </c>
       <c r="B393" t="s">
         <v>1</v>
@@ -4767,23 +4910,23 @@
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A394" t="s">
-        <v>399</v>
+        <v>182</v>
       </c>
       <c r="B394" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A395" t="s">
-        <v>400</v>
+        <v>187</v>
       </c>
       <c r="B395" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A396" t="s">
-        <v>401</v>
+        <v>202</v>
       </c>
       <c r="B396" t="s">
         <v>1</v>
@@ -4791,14 +4934,222 @@
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A397" t="s">
-        <v>402</v>
+        <v>189</v>
       </c>
       <c r="B397" t="s">
-        <v>3</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A398" t="s">
+        <v>204</v>
+      </c>
+      <c r="B398" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A399" t="s">
+        <v>197</v>
+      </c>
+      <c r="B399" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A400" t="s">
+        <v>206</v>
+      </c>
+      <c r="B400" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A401" t="s">
+        <v>386</v>
+      </c>
+      <c r="B401" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A402" t="s">
+        <v>224</v>
+      </c>
+      <c r="B402" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A403" t="s">
+        <v>228</v>
+      </c>
+      <c r="B403" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A404" t="s">
+        <v>235</v>
+      </c>
+      <c r="B404" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A405" t="s">
+        <v>237</v>
+      </c>
+      <c r="B405" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A406" t="s">
+        <v>250</v>
+      </c>
+      <c r="B406" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A407" t="s">
+        <v>393</v>
+      </c>
+      <c r="B407" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A408" t="s">
+        <v>259</v>
+      </c>
+      <c r="B408" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A409" t="s">
+        <v>408</v>
+      </c>
+      <c r="B409" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A410" t="s">
+        <v>277</v>
+      </c>
+      <c r="B410" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A411" t="s">
+        <v>414</v>
+      </c>
+      <c r="B411" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A412" t="s">
+        <v>284</v>
+      </c>
+      <c r="B412" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A413" t="s">
+        <v>303</v>
+      </c>
+      <c r="B413" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A414" t="s">
+        <v>289</v>
+      </c>
+      <c r="B414" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A415" t="s">
+        <v>415</v>
+      </c>
+      <c r="B415" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A416" t="s">
+        <v>300</v>
+      </c>
+      <c r="B416" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A417" t="s">
+        <v>417</v>
+      </c>
+      <c r="B417" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A418" t="s">
+        <v>418</v>
+      </c>
+      <c r="B418" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A419" t="s">
+        <v>305</v>
+      </c>
+      <c r="B419" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A420" t="s">
+        <v>308</v>
+      </c>
+      <c r="B420" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A421" t="s">
+        <v>309</v>
+      </c>
+      <c r="B421" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A422" t="s">
+        <v>322</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B454">
+    <sortCondition ref="B438:B454"/>
+  </sortState>
   <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" sqref="B1175:B1176 B1408:B1421 B1208:B1209 B1212 B1215:B1224 B1234 B1247:B1248 B1260:B1267 B1282:B1287 B1295:B1298 B1311:B1328 B1331:B1338 B1340:B1405 B425:B451 B397:B398 B403:B416 B418 B420:B421 B6:B40 B1:B4" xr:uid="{81BDDD60-04A0-4976-8349-4CA849C03923}">
+      <formula1>"X,F,XF,S,S(RH-),不明"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/bloodtype.xlsx
+++ b/data/bloodtype.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{251ACDBA-E000-413C-B896-2CC8A317F440}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C1D685E-F47D-4C5F-B6AA-DF896D8385E3}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="11955" windowHeight="13170" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
+    <workbookView xWindow="10965" yWindow="2415" windowWidth="9060" windowHeight="13170" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -969,12 +969,6 @@
     <t>ヤマト</t>
   </si>
   <si>
-    <t>ホールデム</t>
-  </si>
-  <si>
-    <t>スピード</t>
-  </si>
-  <si>
     <t>S-スネーク</t>
   </si>
   <si>
@@ -1390,6 +1384,14 @@
     <rPh sb="0" eb="2">
       <t>クジャク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スピード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホールデム</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1766,18 +1768,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -1790,15 +1792,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
@@ -1814,7 +1816,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B7" t="s">
         <v>0</v>
@@ -1894,7 +1896,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B17" t="s">
         <v>0</v>
@@ -1950,7 +1952,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B24" t="s">
         <v>0</v>
@@ -1958,7 +1960,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B25" t="s">
         <v>0</v>
@@ -1974,7 +1976,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B27" t="s">
         <v>0</v>
@@ -2062,15 +2064,15 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s">
         <v>0</v>
@@ -2078,7 +2080,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s">
         <v>0</v>
@@ -2137,7 +2139,7 @@
         <v>267</v>
       </c>
       <c r="B47" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
@@ -2182,7 +2184,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B53" t="s">
         <v>0</v>
@@ -2190,7 +2192,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B54" t="s">
         <v>0</v>
@@ -2206,10 +2208,10 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B56" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.4">
@@ -2230,7 +2232,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B59" t="s">
         <v>0</v>
@@ -2238,7 +2240,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B60" t="s">
         <v>0</v>
@@ -2246,15 +2248,15 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B61" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B62" t="s">
         <v>0</v>
@@ -2262,7 +2264,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B63" t="s">
         <v>0</v>
@@ -2270,7 +2272,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B64" t="s">
         <v>0</v>
@@ -2350,7 +2352,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B74" t="s">
         <v>0</v>
@@ -2414,10 +2416,10 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B82" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
@@ -2502,10 +2504,10 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B93" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
@@ -2518,7 +2520,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B95" t="s">
         <v>0</v>
@@ -2526,7 +2528,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B96" t="s">
         <v>0</v>
@@ -2534,7 +2536,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B97" t="s">
         <v>0</v>
@@ -2582,7 +2584,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B103" t="s">
         <v>0</v>
@@ -2590,7 +2592,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B104" t="s">
         <v>0</v>
@@ -2598,7 +2600,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>312</v>
+        <v>431</v>
       </c>
       <c r="B105" t="s">
         <v>0</v>
@@ -2641,7 +2643,7 @@
         <v>295</v>
       </c>
       <c r="B110" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.4">
@@ -2657,7 +2659,7 @@
         <v>298</v>
       </c>
       <c r="B112" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.4">
@@ -2678,26 +2680,26 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B115" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B116" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B117" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.4">
@@ -2705,7 +2707,7 @@
         <v>306</v>
       </c>
       <c r="B118" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.4">
@@ -2718,7 +2720,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B120" t="s">
         <v>0</v>
@@ -2726,7 +2728,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B121" t="s">
         <v>0</v>
@@ -2734,7 +2736,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B122" t="s">
         <v>0</v>
@@ -2742,7 +2744,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B123" t="s">
         <v>4</v>
@@ -2750,7 +2752,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B124" t="s">
         <v>4</v>
@@ -2758,10 +2760,10 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B125" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.4">
@@ -2822,7 +2824,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B133" t="s">
         <v>4</v>
@@ -2862,7 +2864,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B138" t="s">
         <v>4</v>
@@ -2910,7 +2912,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B144" t="s">
         <v>4</v>
@@ -2934,18 +2936,18 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B147" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B148" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.4">
@@ -2982,7 +2984,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B153" t="s">
         <v>4</v>
@@ -3046,23 +3048,23 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B161" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B162" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B163" t="s">
         <v>4</v>
@@ -3110,7 +3112,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B169" t="s">
         <v>4</v>
@@ -3142,7 +3144,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B173" t="s">
         <v>4</v>
@@ -3166,7 +3168,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B176" t="s">
         <v>4</v>
@@ -3174,7 +3176,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B177" t="s">
         <v>4</v>
@@ -3198,7 +3200,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B180" t="s">
         <v>4</v>
@@ -3206,7 +3208,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B181" t="s">
         <v>4</v>
@@ -3214,7 +3216,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B182" t="s">
         <v>4</v>
@@ -3382,7 +3384,7 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B203" t="s">
         <v>4</v>
@@ -3422,7 +3424,7 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B208" t="s">
         <v>4</v>
@@ -3433,12 +3435,12 @@
         <v>301</v>
       </c>
       <c r="B209" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B210" t="s">
         <v>4</v>
@@ -3486,15 +3488,15 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B216" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B217" t="s">
         <v>4</v>
@@ -3534,7 +3536,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B222" t="s">
         <v>4</v>
@@ -3553,7 +3555,7 @@
         <v>302</v>
       </c>
       <c r="B224" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.4">
@@ -3577,7 +3579,7 @@
         <v>299</v>
       </c>
       <c r="B227" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.4">
@@ -3585,12 +3587,12 @@
         <v>307</v>
       </c>
       <c r="B228" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B229" t="s">
         <v>4</v>
@@ -3598,15 +3600,15 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B230" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B231" t="s">
         <v>4</v>
@@ -3614,7 +3616,7 @@
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B232" t="s">
         <v>4</v>
@@ -3622,7 +3624,7 @@
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B233" t="s">
         <v>4</v>
@@ -3630,7 +3632,7 @@
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B234" t="s">
         <v>4</v>
@@ -3638,7 +3640,7 @@
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B235" t="s">
         <v>4</v>
@@ -3646,7 +3648,7 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B236" t="s">
         <v>4</v>
@@ -3654,7 +3656,7 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B237" t="s">
         <v>4</v>
@@ -3662,7 +3664,7 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B238" t="s">
         <v>4</v>
@@ -3670,7 +3672,7 @@
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B239" t="s">
         <v>4</v>
@@ -3718,7 +3720,7 @@
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B245" t="s">
         <v>194</v>
@@ -3726,7 +3728,7 @@
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B246" t="s">
         <v>194</v>
@@ -3734,15 +3736,15 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B247" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B248" t="s">
         <v>194</v>
@@ -3753,12 +3755,12 @@
         <v>2</v>
       </c>
       <c r="B249" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A250" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B250" t="s">
         <v>3</v>
@@ -3774,7 +3776,7 @@
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B252" t="s">
         <v>3</v>
@@ -3902,7 +3904,7 @@
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B268" t="s">
         <v>3</v>
@@ -3950,18 +3952,18 @@
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B274" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B275" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.4">
@@ -4078,7 +4080,7 @@
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B290" t="s">
         <v>3</v>
@@ -4110,7 +4112,7 @@
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B294" t="s">
         <v>3</v>
@@ -4134,7 +4136,7 @@
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B297" t="s">
         <v>3</v>
@@ -4222,7 +4224,7 @@
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A308" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B308" t="s">
         <v>3</v>
@@ -4318,10 +4320,10 @@
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A320" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B320" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.4">
@@ -4334,7 +4336,7 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A322" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B322" t="s">
         <v>3</v>
@@ -4358,7 +4360,7 @@
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B325" t="s">
         <v>3</v>
@@ -4422,7 +4424,7 @@
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B333" t="s">
         <v>3</v>
@@ -4438,7 +4440,7 @@
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A335" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B335" t="s">
         <v>3</v>
@@ -4470,7 +4472,7 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A339" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B339" t="s">
         <v>3</v>
@@ -4478,7 +4480,7 @@
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A340" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B340" t="s">
         <v>3</v>
@@ -4486,7 +4488,7 @@
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A341" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B341" t="s">
         <v>3</v>
@@ -4494,7 +4496,7 @@
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A342" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B342" t="s">
         <v>3</v>
@@ -4502,7 +4504,7 @@
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A343" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B343" t="s">
         <v>3</v>
@@ -4510,7 +4512,7 @@
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A344" t="s">
-        <v>311</v>
+        <v>430</v>
       </c>
       <c r="B344" t="s">
         <v>3</v>
@@ -4529,7 +4531,7 @@
         <v>304</v>
       </c>
       <c r="B346" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.4">
@@ -4545,7 +4547,7 @@
         <v>294</v>
       </c>
       <c r="B348" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.4">
@@ -4553,7 +4555,7 @@
         <v>296</v>
       </c>
       <c r="B349" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.4">
@@ -4566,10 +4568,10 @@
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A351" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B351" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.4">
@@ -4582,7 +4584,7 @@
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A353" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B353" t="s">
         <v>3</v>
@@ -4590,7 +4592,7 @@
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A354" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B354" t="s">
         <v>3</v>
@@ -4598,7 +4600,7 @@
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A355" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B355" t="s">
         <v>3</v>
@@ -4606,7 +4608,7 @@
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A356" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B356" t="s">
         <v>3</v>
@@ -4614,7 +4616,7 @@
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A357" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B357" t="s">
         <v>3</v>
@@ -4622,10 +4624,10 @@
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A358" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B358" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.4">
@@ -4638,7 +4640,7 @@
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A360" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B360" t="s">
         <v>1</v>
@@ -4782,7 +4784,7 @@
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A378" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B378" t="s">
         <v>1</v>
@@ -4846,7 +4848,7 @@
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A386" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B386" t="s">
         <v>1</v>
@@ -4862,7 +4864,7 @@
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A388" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B388" t="s">
         <v>1</v>
@@ -4878,7 +4880,7 @@
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A390" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B390" t="s">
         <v>1</v>
@@ -4966,7 +4968,7 @@
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A401" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B401" t="s">
         <v>1</v>
@@ -5014,7 +5016,7 @@
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A407" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B407" t="s">
         <v>1</v>
@@ -5030,7 +5032,7 @@
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A409" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B409" t="s">
         <v>1</v>
@@ -5046,7 +5048,7 @@
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A411" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B411" t="s">
         <v>1</v>
@@ -5065,7 +5067,7 @@
         <v>303</v>
       </c>
       <c r="B413" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.4">
@@ -5078,7 +5080,7 @@
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A415" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B415" t="s">
         <v>1</v>
@@ -5089,23 +5091,23 @@
         <v>300</v>
       </c>
       <c r="B416" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A417" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A418" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.4">
@@ -5113,7 +5115,7 @@
         <v>305</v>
       </c>
       <c r="B419" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.4">
@@ -5129,12 +5131,12 @@
         <v>309</v>
       </c>
       <c r="B421" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A422" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B422" t="s">
         <v>1</v>

--- a/data/bloodtype.xlsx
+++ b/data/bloodtype.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C1D685E-F47D-4C5F-B6AA-DF896D8385E3}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{0B1E45A7-EE1E-4D77-BA5F-1D4FF2FD0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55FD91B2-FE52-457E-9556-D32C086CA31C}"/>
   <bookViews>
-    <workbookView xWindow="10965" yWindow="2415" windowWidth="9060" windowHeight="13170" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="9060" windowHeight="13170" xr2:uid="{287E67A6-5940-48A6-8260-952100332F85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3435,7 +3435,7 @@
         <v>301</v>
       </c>
       <c r="B209" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.4">
